--- a/1_Data/Hu_2020_CollabraPsy/Codebook_Hu_2020_CollabraPsy_Exp1_Clean.xlsx
+++ b/1_Data/Hu_2020_CollabraPsy/Codebook_Hu_2020_CollabraPsy_Exp1_Clean.xlsx
@@ -2,382 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -385,323 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1054,6 +403,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1064,31 +414,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col width="30.9090909090909" customWidth="1" min="1" max="1"/>
-    <col width="98.3636363636364" customWidth="1" min="2" max="2"/>
-    <col width="51.1818181818182" customWidth="1" min="3" max="3"/>
-    <col width="21.3636363636364" customWidth="1" min="4" max="4"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Variable_description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Variable_value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Variable_category</t>
         </is>
@@ -1141,12 +485,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bin</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Trial number within the block</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1163,39 +507,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trial number within the block</t>
+          <t>Visual shape stimulus presented in the trial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>immoralSelf;moralOther;immoralOther;moralSelf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visual shape stimulus presented in the trial</t>
+          <t>Text label presented for matching with the shape</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>immoralSelf;moralOther;immoralOther;moralSelf</t>
+          <t>immoralOther;moralSelf;moralOther;immoralSelf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1207,17 +551,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Text label presented for matching with the shape</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>immoralOther;moralSelf;moralOther;immoralSelf</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1251,34 +595,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Morality</t>
+          <t>Label_Origin_Identity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Original identity associated with the label</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Stranger;Self</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
+          <t>Label_English_Identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Original identity associated with the label</t>
+          <t>English translation of the label's identity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1295,12 +639,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
+          <t>Label_Standardized_Identity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>English translation of the label's identity</t>
+          <t>Standardized identity for the label used across experiments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1317,17 +661,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
+          <t>Shape_Origin_Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standardized identity for the label used across experiments</t>
+          <t>Original identity associated with the shape stimulus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stranger;Self</t>
+          <t>Self;Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1339,12 +683,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
+          <t>Shape_English_Identity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Original identity associated with the shape stimulus</t>
+          <t>English translation of the shape's identity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1361,17 +705,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
+          <t>Shape_Standardized_Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>English translation of the shape's identity</t>
+          <t>Standardized identity for the shape used across experiments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Self;Other</t>
+          <t>Self;Stranger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1383,17 +727,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
+          <t>extraIV1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Standardized identity for the shape used across experiments</t>
+          <t>Morality of the stimulus label, fully crossed with Self/Other identity: Good vs Bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Self;Stranger</t>
+          <t>Bad;Good</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/1_Data/Hu_2020_CollabraPsy/Codebook_Hu_2020_CollabraPsy_Exp1_Clean.xlsx
+++ b/1_Data/Hu_2020_CollabraPsy/Codebook_Hu_2020_CollabraPsy_Exp1_Clean.xlsx
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Block number in the experiment; each block may contain practice or experimental trials</t>
+          <t>Block number in the matching task. Blocks 1-3 = formal blocks (120 trials each); Blocks 4-8 = five interleaved short matching blocks of 48 trials each (per paper 'five short interleaved perceptual-matching blocks of 48 trials'). Original program mis-coded blocks 4-8 as Block 1 (recoded 2026-09-02 by time order, 48 rows per block). Subjects 7302/7303 have blocks 1-3 only (no interleaved blocks).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>1-8 (Number)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Trial number within the block</t>
+          <t>Trial number within the block. Bin dimension merged into Trial (Trial = (Bin-1)*24 + Trial, recoded 2026-09-01/02): blocks 1-3 have Trials 1-120, blocks 4-8 have Trials 1-48.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>1-120 (blocks 1-3); 1-48 (blocks 4-8)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
